--- a/RaidenDemo/文档/配置表/BulletResource.xlsx
+++ b/RaidenDemo/文档/配置表/BulletResource.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3a55004f6d294339"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R386a13d4d81349c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,6 +13,7 @@
     <x:author>tc={57593611-C053-B41E-2E62-56E7E934DB06}</x:author>
     <x:author>tc={C20DB847-4AE0-0527-D739-C8B98626858C}</x:author>
     <x:author>tc={5AFFD537-5368-2F7E-AA2F-DE3A20C5C4F6}</x:author>
+    <x:author>tc={486C836A-10CF-2ED3-7D14-F388F8B2FC07}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="C1" authorId="0">
@@ -47,6 +48,16 @@
         </x:r>
       </x:text>
     </x:comment>
+    <x:comment ref="S5" authorId="3">
+      <x:text>
+        <x:r>
+          <x:t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    留空表示不播放子弹发射特效；填写时引用特效表中类型为“子弹发射特效”的有效ID。</x:t>
+        </x:r>
+      </x:text>
+    </x:comment>
   </x:commentList>
 </x:comments>
 </file>
@@ -63,7 +74,7 @@
     <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </x:numFmts>
-  <x:fonts count="24">
+  <x:fonts count="30">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -191,8 +202,38 @@
       <x:sz val="10"/>
       <x:name val="宋体"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFBDD7EE"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFBDD7EE"/>
+      <x:name val="微软雅黑"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="微软雅黑"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="微软雅黑"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="39">
+  <x:fills count="51">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -367,6 +408,66 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor theme="9" tint="0.39998"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF000000"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF404040"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF000000"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF404040"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF000000"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF404040"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF000000"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF404040"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -631,7 +732,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="66">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -679,6 +780,138 @@
     <x:xf numFmtId="0" fontId="3" fillId="38" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="38" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="40" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="40" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="40" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="40" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="41" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="41" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="42" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="43" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="44" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="44" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="45" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="46" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="47" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="3" fillId="47" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="47" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="47" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="48" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="48" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="48" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="49" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="49" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="49" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="50" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="3" fillId="50" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="50" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="50" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="50" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="29" fillId="50" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="29" fillId="50" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
@@ -935,6 +1168,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:person displayName="User" id="{CD55B0ED-1552-4ACF-B04F-BBE0236982D7}"/>
   <xltc:person displayName="tc={57593611-C053-B41E-2E62-56E7E934DB06}" id="{BCD35C28-EA57-CD5E-2173-53DE3C27FD70}"/>
   <xltc:person displayName="tc={C20DB847-4AE0-0527-D739-C8B98626858C}" id="{269C4EE3-3881-5DB1-60AB-31F615A956E4}"/>
   <xltc:person displayName="tc={5AFFD537-5368-2F7E-AA2F-DE3A20C5C4F6}" id="{14D9D3F1-13C8-1348-8190-D5BA0E11AF34}"/>
@@ -1132,6 +1366,14 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
+<xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+  <xltc:threadedComment ref="S5" dT="2026-08-26T12:37:21.535" personId="{CD55B0ED-1552-4ACF-B04F-BBE0236982D7}" id="{486C836A-10CF-2ED3-7D14-F388F8B2FC07}">
+    <xltc:text>留空表示不播放子弹发射特效；填写时引用特效表中类型为“子弹发射特效”的有效ID。</xltc:text>
+  </xltc:threadedComment>
+</xltc:ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -1152,1016 +1394,1048 @@
     <x:col min="16" max="16" width="15" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="22" hidden="0" customWidth="1"/>
     <x:col min="18" max="19" width="24" customWidth="1"/>
-    <x:col min="20" max="20" width="16" customWidth="1"/>
+    <x:col min="20" max="20" width="14" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="24" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="14" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="20" customHeight="1">
-      <x:c r="A1" s="1" t="str">
+      <x:c r="A1" s="55" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="str">
+      <x:c r="B1" s="55" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="str">
+      <x:c r="C1" s="55" t="str">
         <x:v>code</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="str">
+      <x:c r="D1" s="55" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="str">
+      <x:c r="E1" s="55" t="str">
         <x:v>bullet</x:v>
       </x:c>
-      <x:c r="F1" s="1"/>
-      <x:c r="G1" s="1"/>
-      <x:c r="H1" s="1"/>
-      <x:c r="I1" s="1"/>
-      <x:c r="J1" s="1"/>
-      <x:c r="K1" s="1"/>
-      <x:c r="L1" s="1"/>
-      <x:c r="M1" s="1"/>
-      <x:c r="N1" s="1"/>
-      <x:c r="O1" s="6"/>
-      <x:c r="P1" s="6"/>
-      <x:c r="Q1" s="6"/>
-      <x:c r="R1" s="6"/>
-      <x:c r="S1" s="6" t="str">
+      <x:c r="F1" s="55"/>
+      <x:c r="G1" s="55"/>
+      <x:c r="H1" s="55"/>
+      <x:c r="I1" s="55"/>
+      <x:c r="J1" s="55"/>
+      <x:c r="K1" s="55"/>
+      <x:c r="L1" s="55"/>
+      <x:c r="M1" s="55"/>
+      <x:c r="N1" s="55"/>
+      <x:c r="O1" s="55"/>
+      <x:c r="P1" s="55"/>
+      <x:c r="Q1" s="55"/>
+      <x:c r="R1" s="55"/>
+      <x:c r="S1" s="55"/>
+      <x:c r="T1" s="55" t="str">
         <x:v>poolCapacity</x:v>
       </x:c>
-      <x:c r="T1"/>
     </x:row>
     <x:row r="2" ht="20" customHeight="1">
-      <x:c r="A2" s="2" t="str">
+      <x:c r="A2" s="58" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B2" s="2" t="str">
+      <x:c r="B2" s="58" t="str">
         <x:v>子弹ID</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="str">
+      <x:c r="C2" s="58" t="str">
         <x:v>稳定编码</x:v>
       </x:c>
-      <x:c r="D2" s="2" t="str">
+      <x:c r="D2" s="58" t="str">
         <x:v>子弹说明</x:v>
       </x:c>
-      <x:c r="E2" s="2" t="str">
+      <x:c r="E2" s="58" t="str">
         <x:v>子弹本体</x:v>
       </x:c>
-      <x:c r="F2" s="2"/>
-      <x:c r="G2" s="2"/>
-      <x:c r="H2" s="2"/>
-      <x:c r="I2" s="2"/>
-      <x:c r="J2" s="2"/>
-      <x:c r="K2" s="2"/>
-      <x:c r="L2" s="2"/>
-      <x:c r="M2" s="2"/>
-      <x:c r="N2" s="2"/>
-      <x:c r="O2" s="11"/>
-      <x:c r="P2" s="11"/>
-      <x:c r="Q2" s="11"/>
-      <x:c r="R2" s="11"/>
-      <x:c r="S2" s="11" t="str">
+      <x:c r="F2" s="58"/>
+      <x:c r="G2" s="58"/>
+      <x:c r="H2" s="58"/>
+      <x:c r="I2" s="58"/>
+      <x:c r="J2" s="58"/>
+      <x:c r="K2" s="58"/>
+      <x:c r="L2" s="58"/>
+      <x:c r="M2" s="58"/>
+      <x:c r="N2" s="58"/>
+      <x:c r="O2" s="58"/>
+      <x:c r="P2" s="58"/>
+      <x:c r="Q2" s="58"/>
+      <x:c r="R2" s="58"/>
+      <x:c r="S2" s="58"/>
+      <x:c r="T2" s="58" t="str">
         <x:v>对象池容量</x:v>
       </x:c>
-      <x:c r="T2"/>
     </x:row>
     <x:row r="3" ht="20" customHeight="1">
-      <x:c r="A3" s="1" t="str">
+      <x:c r="A3" s="55" t="str">
         <x:v>##type</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="str">
+      <x:c r="B3" s="55" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="str">
+      <x:c r="C3" s="55" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D3" s="1"/>
-      <x:c r="E3" s="1" t="str">
+      <x:c r="D3" s="55"/>
+      <x:c r="E3" s="55" t="str">
         <x:v>Bullet</x:v>
       </x:c>
-      <x:c r="F3" s="1"/>
-      <x:c r="G3" s="1"/>
-      <x:c r="H3" s="1"/>
-      <x:c r="I3" s="1"/>
-      <x:c r="J3" s="1"/>
-      <x:c r="K3" s="1"/>
-      <x:c r="L3" s="1"/>
-      <x:c r="M3" s="1"/>
-      <x:c r="N3" s="1"/>
-      <x:c r="O3" s="6"/>
-      <x:c r="P3" s="6"/>
-      <x:c r="Q3" s="6"/>
-      <x:c r="R3" s="6"/>
-      <x:c r="S3" s="6" t="str">
+      <x:c r="F3" s="55"/>
+      <x:c r="G3" s="55"/>
+      <x:c r="H3" s="55"/>
+      <x:c r="I3" s="55"/>
+      <x:c r="J3" s="55"/>
+      <x:c r="K3" s="55"/>
+      <x:c r="L3" s="55"/>
+      <x:c r="M3" s="55"/>
+      <x:c r="N3" s="55"/>
+      <x:c r="O3" s="55"/>
+      <x:c r="P3" s="55"/>
+      <x:c r="Q3" s="55"/>
+      <x:c r="R3" s="55"/>
+      <x:c r="S3" s="55"/>
+      <x:c r="T3" s="55" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="T3"/>
     </x:row>
     <x:row r="4" ht="20" customHeight="1">
-      <x:c r="A4" s="1" t="str">
+      <x:c r="A4" s="55" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B4" s="1"/>
-      <x:c r="C4" s="1"/>
-      <x:c r="D4" s="1"/>
-      <x:c r="E4" s="1" t="str">
+      <x:c r="B4" s="55"/>
+      <x:c r="C4" s="55"/>
+      <x:c r="D4" s="55"/>
+      <x:c r="E4" s="55" t="str">
         <x:v>appearanceType</x:v>
       </x:c>
-      <x:c r="F4" s="1" t="str">
+      <x:c r="F4" s="55" t="str">
         <x:v>appearancePath</x:v>
       </x:c>
-      <x:c r="G4" s="1" t="str">
+      <x:c r="G4" s="55" t="str">
         <x:v>shape</x:v>
       </x:c>
-      <x:c r="H4" s="1"/>
-      <x:c r="I4" s="1"/>
-      <x:c r="J4" s="1"/>
-      <x:c r="K4" s="1" t="str">
+      <x:c r="H4" s="55"/>
+      <x:c r="I4" s="55"/>
+      <x:c r="J4" s="55"/>
+      <x:c r="K4" s="55" t="str">
         <x:v>motionType</x:v>
       </x:c>
-      <x:c r="L4" s="1" t="str">
+      <x:c r="L4" s="55" t="str">
         <x:v>rotate</x:v>
       </x:c>
-      <x:c r="M4" s="1" t="str">
+      <x:c r="M4" s="55" t="str">
         <x:v>rotationSpeed</x:v>
       </x:c>
-      <x:c r="N4" s="1" t="str">
+      <x:c r="N4" s="55" t="str">
         <x:v>speed</x:v>
       </x:c>
-      <x:c r="O4" s="6" t="str">
+      <x:c r="O4" s="55" t="str">
         <x:v>damage</x:v>
       </x:c>
-      <x:c r="P4" s="6" t="str">
+      <x:c r="P4" s="55" t="str">
         <x:v>hitEffectId</x:v>
       </x:c>
-      <x:c r="Q4" s="6" t="str">
+      <x:c r="Q4" s="55" t="str">
         <x:v>trackingDelayMs</x:v>
       </x:c>
-      <x:c r="R4" s="6" t="str">
+      <x:c r="R4" s="55" t="str">
         <x:v>trackingTurnSpeed</x:v>
       </x:c>
-      <x:c r="S4" s="6"/>
-      <x:c r="T4"/>
+      <x:c r="S4" s="55" t="str">
+        <x:v>launchEffectId</x:v>
+      </x:c>
+      <x:c r="T4" s="55"/>
     </x:row>
     <x:row r="5" ht="17.25">
-      <x:c r="A5" s="2" t="str">
+      <x:c r="A5" s="58" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B5" s="2"/>
-      <x:c r="C5" s="2"/>
-      <x:c r="D5" s="2"/>
-      <x:c r="E5" s="2" t="str">
+      <x:c r="B5" s="58"/>
+      <x:c r="C5" s="58"/>
+      <x:c r="D5" s="58"/>
+      <x:c r="E5" s="58" t="str">
         <x:v>外观类型</x:v>
       </x:c>
-      <x:c r="F5" s="2" t="str">
+      <x:c r="F5" s="58" t="str">
         <x:v>外观资源相对路径</x:v>
       </x:c>
-      <x:c r="G5" s="2" t="str">
+      <x:c r="G5" s="58" t="str">
         <x:v>形状</x:v>
       </x:c>
-      <x:c r="H5" s="2"/>
-      <x:c r="I5" s="2"/>
-      <x:c r="J5" s="2"/>
-      <x:c r="K5" s="2" t="str">
+      <x:c r="H5" s="58"/>
+      <x:c r="I5" s="58"/>
+      <x:c r="J5" s="58"/>
+      <x:c r="K5" s="58" t="str">
         <x:v>行动方式</x:v>
       </x:c>
-      <x:c r="L5" s="2" t="str">
+      <x:c r="L5" s="58" t="str">
         <x:v>是否自转</x:v>
       </x:c>
-      <x:c r="M5" s="2" t="str">
+      <x:c r="M5" s="58" t="str">
         <x:v>自转速度</x:v>
       </x:c>
-      <x:c r="N5" s="2" t="str">
+      <x:c r="N5" s="58" t="str">
         <x:v>飞行速度</x:v>
       </x:c>
-      <x:c r="O5" s="11" t="str">
+      <x:c r="O5" s="58" t="str">
         <x:v>伤害</x:v>
       </x:c>
-      <x:c r="P5" s="11" t="str">
+      <x:c r="P5" s="58" t="str">
         <x:v>命中特效ID</x:v>
       </x:c>
-      <x:c r="Q5" s="11" t="str">
+      <x:c r="Q5" s="58" t="str">
         <x:v>跟踪锁定延迟（毫秒）</x:v>
       </x:c>
-      <x:c r="R5" s="11" t="str">
+      <x:c r="R5" s="58" t="str">
         <x:v>跟踪转向速度（度/秒）</x:v>
       </x:c>
-      <x:c r="S5" s="11"/>
-      <x:c r="T5"/>
+      <x:c r="S5" s="58" t="str">
+        <x:v>发射特效ID</x:v>
+      </x:c>
+      <x:c r="T5" s="58"/>
     </x:row>
     <x:row r="6" ht="17.25">
-      <x:c r="A6" s="1" t="str">
+      <x:c r="A6" s="55" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B6" s="1"/>
-      <x:c r="C6" s="1"/>
-      <x:c r="D6" s="1"/>
-      <x:c r="E6" s="1"/>
-      <x:c r="F6" s="1"/>
-      <x:c r="G6" s="1" t="str">
+      <x:c r="B6" s="55"/>
+      <x:c r="C6" s="55"/>
+      <x:c r="D6" s="55"/>
+      <x:c r="E6" s="55"/>
+      <x:c r="F6" s="55"/>
+      <x:c r="G6" s="55" t="str">
         <x:v>$type</x:v>
       </x:c>
-      <x:c r="H6" s="1" t="str">
+      <x:c r="H6" s="55" t="str">
         <x:v>radius</x:v>
       </x:c>
-      <x:c r="I6" s="1" t="str">
+      <x:c r="I6" s="55" t="str">
         <x:v>rect</x:v>
       </x:c>
-      <x:c r="J6" s="1" t="str">
+      <x:c r="J6" s="55" t="str">
         <x:v>pivot</x:v>
       </x:c>
-      <x:c r="K6" s="1"/>
-      <x:c r="L6" s="1"/>
-      <x:c r="M6" s="1"/>
-      <x:c r="N6" s="1"/>
-      <x:c r="O6" s="6"/>
-      <x:c r="P6" s="6"/>
-      <x:c r="Q6" s="6"/>
-      <x:c r="R6" s="6"/>
-      <x:c r="S6" s="6"/>
-      <x:c r="T6"/>
+      <x:c r="K6" s="55"/>
+      <x:c r="L6" s="55"/>
+      <x:c r="M6" s="55"/>
+      <x:c r="N6" s="55"/>
+      <x:c r="O6" s="55"/>
+      <x:c r="P6" s="55"/>
+      <x:c r="Q6" s="55"/>
+      <x:c r="R6" s="55"/>
+      <x:c r="S6" s="55"/>
+      <x:c r="T6" s="55"/>
     </x:row>
     <x:row r="7" ht="17.25">
-      <x:c r="A7" s="3"/>
-      <x:c r="B7" s="3" t="n">
+      <x:c r="A7" s="63"/>
+      <x:c r="B7" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="str">
+      <x:c r="C7" s="63" t="str">
         <x:v>enemy_small</x:v>
       </x:c>
-      <x:c r="D7" s="3" t="str">
+      <x:c r="D7" s="63" t="str">
         <x:v>敌方通用小型直线弹</x:v>
       </x:c>
-      <x:c r="E7" s="3" t="str">
+      <x:c r="E7" s="63" t="str">
         <x:v>图片</x:v>
       </x:c>
-      <x:c r="F7" s="3" t="str">
+      <x:c r="F7" s="63" t="str">
         <x:v>bullet/enemy/battleEnemyBullet</x:v>
       </x:c>
-      <x:c r="G7" s="3" t="str">
+      <x:c r="G7" s="63" t="str">
         <x:v>矩形</x:v>
       </x:c>
-      <x:c r="H7" s="4"/>
-      <x:c r="I7" s="4" t="str">
+      <x:c r="H7" s="64"/>
+      <x:c r="I7" s="64" t="str">
         <x:v>14,14</x:v>
       </x:c>
-      <x:c r="J7" s="3" t="str">
+      <x:c r="J7" s="63" t="str">
         <x:v>0.5,0.5</x:v>
       </x:c>
-      <x:c r="K7" s="3" t="str">
+      <x:c r="K7" s="63" t="str">
         <x:v>直线</x:v>
       </x:c>
-      <x:c r="L7" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M7" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="3" t="n">
+      <x:c r="L7" s="65" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" s="63" t="n">
         <x:v>420</x:v>
       </x:c>
-      <x:c r="O7" s="16" t="n">
+      <x:c r="O7" s="63" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="P7" s="16" t="n">
+      <x:c r="P7" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q7" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R7" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S7" s="16" t="n">
+      <x:c r="Q7" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R7" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S7" s="63" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T7" s="63" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="T7"/>
     </x:row>
     <x:row r="8" ht="17.25">
-      <x:c r="A8" s="3"/>
-      <x:c r="B8" s="3" t="n">
+      <x:c r="A8" s="63"/>
+      <x:c r="B8" s="63" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="str">
+      <x:c r="C8" s="63" t="str">
         <x:v>player_vertical_line</x:v>
       </x:c>
-      <x:c r="D8" s="3" t="str">
+      <x:c r="D8" s="63" t="str">
         <x:v>我方旧版竖直光束弹</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="str">
+      <x:c r="E8" s="63" t="str">
         <x:v>图片</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="str">
+      <x:c r="F8" s="63" t="str">
         <x:v>bullet/self/battlePlayerLaser</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="str">
+      <x:c r="G8" s="63" t="str">
         <x:v>矩形</x:v>
       </x:c>
-      <x:c r="H8" s="4"/>
-      <x:c r="I8" s="4" t="str">
+      <x:c r="H8" s="64"/>
+      <x:c r="I8" s="64" t="str">
         <x:v>14,120</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="str">
+      <x:c r="J8" s="63" t="str">
         <x:v>0.5,0.5</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="str">
+      <x:c r="K8" s="63" t="str">
         <x:v>直线</x:v>
       </x:c>
-      <x:c r="L8" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M8" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="3" t="n">
-        <x:v>1050</x:v>
-      </x:c>
-      <x:c r="O8" s="16" t="n">
+      <x:c r="L8" s="65" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" s="63" t="n">
+        <x:v>3150</x:v>
+      </x:c>
+      <x:c r="O8" s="63" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="P8" s="16" t="n">
+      <x:c r="P8" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="Q8" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R8" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S8" s="16" t="n">
+      <x:c r="Q8" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R8" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S8" s="63" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T8" s="63" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="T8"/>
     </x:row>
     <x:row r="9" ht="17.25">
-      <x:c r="A9" s="3"/>
-      <x:c r="B9" s="3" t="n">
+      <x:c r="A9" s="63"/>
+      <x:c r="B9" s="63" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C9" s="3" t="str">
+      <x:c r="C9" s="63" t="str">
         <x:v>player_tracking</x:v>
       </x:c>
-      <x:c r="D9" s="3" t="str">
+      <x:c r="D9" s="63" t="str">
         <x:v>我方轻型追踪飞镖</x:v>
       </x:c>
-      <x:c r="E9" s="3" t="str">
+      <x:c r="E9" s="63" t="str">
         <x:v>图片</x:v>
       </x:c>
-      <x:c r="F9" s="3" t="str">
+      <x:c r="F9" s="63" t="str">
         <x:v>bullet/self/bullet_tracking_dart</x:v>
       </x:c>
-      <x:c r="G9" s="3" t="str">
+      <x:c r="G9" s="63" t="str">
         <x:v>矩形</x:v>
       </x:c>
-      <x:c r="H9" s="4"/>
-      <x:c r="I9" s="4" t="str">
+      <x:c r="H9" s="64"/>
+      <x:c r="I9" s="64" t="str">
         <x:v>29,27</x:v>
       </x:c>
-      <x:c r="J9" s="3" t="str">
+      <x:c r="J9" s="63" t="str">
         <x:v>0.5,0</x:v>
       </x:c>
-      <x:c r="K9" s="3" t="str">
+      <x:c r="K9" s="63" t="str">
         <x:v>跟踪</x:v>
       </x:c>
-      <x:c r="L9" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M9" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="3" t="n">
+      <x:c r="L9" s="65" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" s="63" t="n">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="O9" s="63" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P9" s="63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q9" s="63" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="R9" s="63" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="S9" s="63" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T9" s="63" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="17.25">
+      <x:c r="A10" s="63"/>
+      <x:c r="B10" s="63" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="63" t="str">
+        <x:v>player_straight_diamond</x:v>
+      </x:c>
+      <x:c r="D10" s="63" t="str">
+        <x:v>短小菱形光弹，适合常规集中射击</x:v>
+      </x:c>
+      <x:c r="E10" s="63" t="str">
+        <x:v>图片</x:v>
+      </x:c>
+      <x:c r="F10" s="63" t="str">
+        <x:v>bullet/self/bullet_straight_light_diamond</x:v>
+      </x:c>
+      <x:c r="G10" s="63" t="str">
+        <x:v>矩形</x:v>
+      </x:c>
+      <x:c r="H10" s="64"/>
+      <x:c r="I10" s="64" t="str">
+        <x:v>12,40</x:v>
+      </x:c>
+      <x:c r="J10" s="63" t="str">
+        <x:v>0.5,0.5</x:v>
+      </x:c>
+      <x:c r="K10" s="63" t="str">
+        <x:v>直线</x:v>
+      </x:c>
+      <x:c r="L10" s="65" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N10" s="63" t="n">
+        <x:v>1350</x:v>
+      </x:c>
+      <x:c r="O10" s="63" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P10" s="63" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="Q10" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R10" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S10" s="63" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T10" s="63" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="17.25">
+      <x:c r="A11" s="63"/>
+      <x:c r="B11" s="63" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C11" s="63" t="str">
+        <x:v>player_straight_heavy_beam</x:v>
+      </x:c>
+      <x:c r="D11" s="63" t="str">
+        <x:v>粗长高伤光束弹，适合重装机体</x:v>
+      </x:c>
+      <x:c r="E11" s="63" t="str">
+        <x:v>图片</x:v>
+      </x:c>
+      <x:c r="F11" s="63" t="str">
+        <x:v>bullet/self/bullet_straight_light_heavy_beam</x:v>
+      </x:c>
+      <x:c r="G11" s="63" t="str">
+        <x:v>矩形</x:v>
+      </x:c>
+      <x:c r="H11" s="64"/>
+      <x:c r="I11" s="64" t="str">
+        <x:v>14,72</x:v>
+      </x:c>
+      <x:c r="J11" s="63" t="str">
+        <x:v>0.5,0.5</x:v>
+      </x:c>
+      <x:c r="K11" s="63" t="str">
+        <x:v>直线</x:v>
+      </x:c>
+      <x:c r="L11" s="65" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N11" s="63" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="O11" s="63" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="P11" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q11" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R11" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S11" s="63" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T11" s="63" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="17.25">
+      <x:c r="A12" s="63"/>
+      <x:c r="B12" s="63" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C12" s="63" t="str">
+        <x:v>player_straight_long_shuttle</x:v>
+      </x:c>
+      <x:c r="D12" s="63" t="str">
+        <x:v>长梭形光弹，兼顾射程感与威力</x:v>
+      </x:c>
+      <x:c r="E12" s="63" t="str">
+        <x:v>图片</x:v>
+      </x:c>
+      <x:c r="F12" s="63" t="str">
+        <x:v>bullet/self/bullet_straight_light_long_shuttle</x:v>
+      </x:c>
+      <x:c r="G12" s="63" t="str">
+        <x:v>矩形</x:v>
+      </x:c>
+      <x:c r="H12" s="64"/>
+      <x:c r="I12" s="64" t="str">
+        <x:v>18,50</x:v>
+      </x:c>
+      <x:c r="J12" s="63" t="str">
+        <x:v>0.5,0.5</x:v>
+      </x:c>
+      <x:c r="K12" s="63" t="str">
+        <x:v>直线</x:v>
+      </x:c>
+      <x:c r="L12" s="65" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" s="63" t="n">
+        <x:v>2700</x:v>
+      </x:c>
+      <x:c r="O12" s="63" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="P12" s="63" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="Q12" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R12" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S12" s="63" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T12" s="63" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="17.25">
+      <x:c r="A13" s="63"/>
+      <x:c r="B13" s="63" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C13" s="63" t="str">
+        <x:v>player_straight_needle</x:v>
+      </x:c>
+      <x:c r="D13" s="63" t="str">
+        <x:v>高速细针光弹，适合高射速机体</x:v>
+      </x:c>
+      <x:c r="E13" s="63" t="str">
+        <x:v>图片</x:v>
+      </x:c>
+      <x:c r="F13" s="63" t="str">
+        <x:v>bullet/self/bullet_straight_light_needle</x:v>
+      </x:c>
+      <x:c r="G13" s="63" t="str">
+        <x:v>矩形</x:v>
+      </x:c>
+      <x:c r="H13" s="64"/>
+      <x:c r="I13" s="64" t="str">
+        <x:v>8,28</x:v>
+      </x:c>
+      <x:c r="J13" s="63" t="str">
+        <x:v>0.5,0.5</x:v>
+      </x:c>
+      <x:c r="K13" s="63" t="str">
+        <x:v>直线</x:v>
+      </x:c>
+      <x:c r="L13" s="65" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="63" t="n">
+        <x:v>1725</x:v>
+      </x:c>
+      <x:c r="O13" s="63" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P13" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q13" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R13" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S13" s="63" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T13" s="63" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="17.25">
+      <x:c r="A14" s="63"/>
+      <x:c r="B14" s="63" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C14" s="63" t="str">
+        <x:v>player_straight_short_shuttle</x:v>
+      </x:c>
+      <x:c r="D14" s="63" t="str">
+        <x:v>短梭形光弹，适合密集连续射击</x:v>
+      </x:c>
+      <x:c r="E14" s="63" t="str">
+        <x:v>图片</x:v>
+      </x:c>
+      <x:c r="F14" s="63" t="str">
+        <x:v>bullet/self/bullet_straight_light_short_shuttle</x:v>
+      </x:c>
+      <x:c r="G14" s="63" t="str">
+        <x:v>矩形</x:v>
+      </x:c>
+      <x:c r="H14" s="64"/>
+      <x:c r="I14" s="64" t="str">
+        <x:v>14,36</x:v>
+      </x:c>
+      <x:c r="J14" s="63" t="str">
+        <x:v>0.5,0.5</x:v>
+      </x:c>
+      <x:c r="K14" s="63" t="str">
+        <x:v>直线</x:v>
+      </x:c>
+      <x:c r="L14" s="65" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N14" s="63" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="O14" s="63" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P14" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q14" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R14" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S14" s="63" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T14" s="63" t="n">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="17.25">
+      <x:c r="A15" s="63"/>
+      <x:c r="B15" s="63" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C15" s="63" t="str">
+        <x:v>player_straight_twin_core</x:v>
+      </x:c>
+      <x:c r="D15" s="63" t="str">
+        <x:v>双核心光弹，适合强化型直线火力</x:v>
+      </x:c>
+      <x:c r="E15" s="63" t="str">
+        <x:v>图片</x:v>
+      </x:c>
+      <x:c r="F15" s="63" t="str">
+        <x:v>bullet/self/bullet_straight_light_twin_core</x:v>
+      </x:c>
+      <x:c r="G15" s="63" t="str">
+        <x:v>矩形</x:v>
+      </x:c>
+      <x:c r="H15" s="64"/>
+      <x:c r="I15" s="64" t="str">
+        <x:v>14,42</x:v>
+      </x:c>
+      <x:c r="J15" s="63" t="str">
+        <x:v>0.5,0.5</x:v>
+      </x:c>
+      <x:c r="K15" s="63" t="str">
+        <x:v>直线</x:v>
+      </x:c>
+      <x:c r="L15" s="65" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="63" t="n">
+        <x:v>1425</x:v>
+      </x:c>
+      <x:c r="O15" s="63" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="P15" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q15" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R15" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S15" s="63" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T15" s="63" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="17.25">
+      <x:c r="A16" s="63"/>
+      <x:c r="B16" s="63" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C16" s="63" t="str">
+        <x:v>player_tracking_dart</x:v>
+      </x:c>
+      <x:c r="D16" s="63" t="str">
+        <x:v>带稳定翼的轻型追踪飞镖</x:v>
+      </x:c>
+      <x:c r="E16" s="63" t="str">
+        <x:v>图片</x:v>
+      </x:c>
+      <x:c r="F16" s="63" t="str">
+        <x:v>bullet/self/bullet_tracking_dart</x:v>
+      </x:c>
+      <x:c r="G16" s="63" t="str">
+        <x:v>矩形</x:v>
+      </x:c>
+      <x:c r="H16" s="64"/>
+      <x:c r="I16" s="64" t="str">
+        <x:v>29,27</x:v>
+      </x:c>
+      <x:c r="J16" s="63" t="str">
+        <x:v>0.5,0</x:v>
+      </x:c>
+      <x:c r="K16" s="63" t="str">
+        <x:v>跟踪</x:v>
+      </x:c>
+      <x:c r="L16" s="65" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" s="63" t="n">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="O16" s="63" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="P16" s="63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q16" s="63" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="R16" s="63" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="S16" s="63" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T16" s="63" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="17.25">
+      <x:c r="A17" s="63"/>
+      <x:c r="B17" s="63" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C17" s="63" t="str">
+        <x:v>player_tracking_micro</x:v>
+      </x:c>
+      <x:c r="D17" s="63" t="str">
+        <x:v>小型高速追踪弹，转向较灵活</x:v>
+      </x:c>
+      <x:c r="E17" s="63" t="str">
+        <x:v>图片</x:v>
+      </x:c>
+      <x:c r="F17" s="63" t="str">
+        <x:v>bullet/self/bullet_tracking_micro</x:v>
+      </x:c>
+      <x:c r="G17" s="63" t="str">
+        <x:v>矩形</x:v>
+      </x:c>
+      <x:c r="H17" s="64"/>
+      <x:c r="I17" s="64" t="str">
+        <x:v>7,16</x:v>
+      </x:c>
+      <x:c r="J17" s="63" t="str">
+        <x:v>0.5,0</x:v>
+      </x:c>
+      <x:c r="K17" s="63" t="str">
+        <x:v>跟踪</x:v>
+      </x:c>
+      <x:c r="L17" s="65" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" s="63" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="O17" s="63" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="P17" s="63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q17" s="63" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="R17" s="63" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="S17" s="63" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T17" s="63" t="n">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="17.25">
+      <x:c r="A18" s="63"/>
+      <x:c r="B18" s="63" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C18" s="63" t="str">
+        <x:v>player_tracking_missile_standard</x:v>
+      </x:c>
+      <x:c r="D18" s="63" t="str">
+        <x:v>标准制式追踪导弹</x:v>
+      </x:c>
+      <x:c r="E18" s="63" t="str">
+        <x:v>图片</x:v>
+      </x:c>
+      <x:c r="F18" s="63" t="str">
+        <x:v>bullet/self/bullet_tracking_missile_standard</x:v>
+      </x:c>
+      <x:c r="G18" s="63" t="str">
+        <x:v>矩形</x:v>
+      </x:c>
+      <x:c r="H18" s="64"/>
+      <x:c r="I18" s="64" t="str">
+        <x:v>17,34</x:v>
+      </x:c>
+      <x:c r="J18" s="63" t="str">
+        <x:v>0.5,0</x:v>
+      </x:c>
+      <x:c r="K18" s="63" t="str">
+        <x:v>跟踪</x:v>
+      </x:c>
+      <x:c r="L18" s="65" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N18" s="63" t="n">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="O9" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="P9" s="16" t="n">
+      <x:c r="O18" s="63" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="P18" s="63" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="Q9" s="16" t="n">
+      <x:c r="Q18" s="63" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="R9" s="16" t="n">
+      <x:c r="R18" s="63" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="S9" s="16" t="n">
+      <x:c r="S18" s="63" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T18" s="63" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="T9"/>
-    </x:row>
-    <x:row r="10" ht="17.25">
-      <x:c r="A10" s="3"/>
-      <x:c r="B10" s="3" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="3" t="str">
-        <x:v>player_straight_diamond</x:v>
-      </x:c>
-      <x:c r="D10" s="3" t="str">
-        <x:v>短小菱形光弹，适合常规集中射击</x:v>
-      </x:c>
-      <x:c r="E10" s="3" t="str">
+    </x:row>
+    <x:row r="19" ht="17.25">
+      <x:c r="A19" s="63"/>
+      <x:c r="B19" s="63" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C19" s="63" t="str">
+        <x:v>player_tracking_torpedo_deep_sea</x:v>
+      </x:c>
+      <x:c r="D19" s="63" t="str">
+        <x:v>大型圆形深海鱼雷，缓慢但伤害较高</x:v>
+      </x:c>
+      <x:c r="E19" s="63" t="str">
         <x:v>图片</x:v>
       </x:c>
-      <x:c r="F10" s="3" t="str">
-        <x:v>bullet/self/bullet_straight_light_diamond</x:v>
-      </x:c>
-      <x:c r="G10" s="3" t="str">
+      <x:c r="F19" s="63" t="str">
+        <x:v>bullet/self/bullet_tracking_torpedo_deep_sea</x:v>
+      </x:c>
+      <x:c r="G19" s="63" t="str">
+        <x:v>圆形</x:v>
+      </x:c>
+      <x:c r="H19" s="64" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I19" s="64"/>
+      <x:c r="J19" s="63"/>
+      <x:c r="K19" s="63" t="str">
+        <x:v>跟踪</x:v>
+      </x:c>
+      <x:c r="L19" s="65" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N19" s="63" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="O19" s="63" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="P19" s="63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q19" s="63" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="R19" s="63" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="S19" s="63" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T19" s="63" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="17.25">
+      <x:c r="A20" s="63"/>
+      <x:c r="B20" s="63" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C20" s="63" t="str">
+        <x:v>player_tracking_torpedo_heavy</x:v>
+      </x:c>
+      <x:c r="D20" s="63" t="str">
+        <x:v>重型鱼雷，速度较慢且威力较高</x:v>
+      </x:c>
+      <x:c r="E20" s="63" t="str">
+        <x:v>图片</x:v>
+      </x:c>
+      <x:c r="F20" s="63" t="str">
+        <x:v>bullet/self/bullet_tracking_torpedo_heavy</x:v>
+      </x:c>
+      <x:c r="G20" s="63" t="str">
         <x:v>矩形</x:v>
       </x:c>
-      <x:c r="H10" s="4"/>
-      <x:c r="I10" s="4" t="str">
-        <x:v>12,40</x:v>
-      </x:c>
-      <x:c r="J10" s="3" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
-      <x:c r="K10" s="3" t="str">
-        <x:v>直线</x:v>
-      </x:c>
-      <x:c r="L10" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M10" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="3" t="n">
-        <x:v>900</x:v>
-      </x:c>
-      <x:c r="O10" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="P10" s="16" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="Q10" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R10" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S10" s="16" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="T10"/>
-    </x:row>
-    <x:row r="11" ht="17.25">
-      <x:c r="A11" s="3"/>
-      <x:c r="B11" s="3" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="3" t="str">
-        <x:v>player_straight_heavy_beam</x:v>
-      </x:c>
-      <x:c r="D11" s="3" t="str">
-        <x:v>粗长高伤光束弹，适合重装机体</x:v>
-      </x:c>
-      <x:c r="E11" s="3" t="str">
-        <x:v>图片</x:v>
-      </x:c>
-      <x:c r="F11" s="3" t="str">
-        <x:v>bullet/self/bullet_straight_light_heavy_beam</x:v>
-      </x:c>
-      <x:c r="G11" s="3" t="str">
-        <x:v>矩形</x:v>
-      </x:c>
-      <x:c r="H11" s="4"/>
-      <x:c r="I11" s="4" t="str">
-        <x:v>14,72</x:v>
-      </x:c>
-      <x:c r="J11" s="3" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
-      <x:c r="K11" s="3" t="str">
-        <x:v>直线</x:v>
-      </x:c>
-      <x:c r="L11" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M11" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="3" t="n">
-        <x:v>800</x:v>
-      </x:c>
-      <x:c r="O11" s="16" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="P11" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q11" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R11" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S11" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="T11"/>
-    </x:row>
-    <x:row r="12" ht="17.25">
-      <x:c r="A12" s="3"/>
-      <x:c r="B12" s="3" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="3" t="str">
-        <x:v>player_straight_long_shuttle</x:v>
-      </x:c>
-      <x:c r="D12" s="3" t="str">
-        <x:v>长梭形光弹，兼顾射程感与威力</x:v>
-      </x:c>
-      <x:c r="E12" s="3" t="str">
-        <x:v>图片</x:v>
-      </x:c>
-      <x:c r="F12" s="3" t="str">
-        <x:v>bullet/self/bullet_straight_light_long_shuttle</x:v>
-      </x:c>
-      <x:c r="G12" s="3" t="str">
-        <x:v>矩形</x:v>
-      </x:c>
-      <x:c r="H12" s="4"/>
-      <x:c r="I12" s="4" t="str">
-        <x:v>18,50</x:v>
-      </x:c>
-      <x:c r="J12" s="3" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
-      <x:c r="K12" s="3" t="str">
-        <x:v>直线</x:v>
-      </x:c>
-      <x:c r="L12" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M12" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="3" t="n">
-        <x:v>900</x:v>
-      </x:c>
-      <x:c r="O12" s="16" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="P12" s="16" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="Q12" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R12" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S12" s="16" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="T12"/>
-    </x:row>
-    <x:row r="13" ht="17.25">
-      <x:c r="A13" s="3"/>
-      <x:c r="B13" s="3" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C13" s="3" t="str">
-        <x:v>player_straight_needle</x:v>
-      </x:c>
-      <x:c r="D13" s="3" t="str">
-        <x:v>高速细针光弹，适合高射速机体</x:v>
-      </x:c>
-      <x:c r="E13" s="3" t="str">
-        <x:v>图片</x:v>
-      </x:c>
-      <x:c r="F13" s="3" t="str">
-        <x:v>bullet/self/bullet_straight_light_needle</x:v>
-      </x:c>
-      <x:c r="G13" s="3" t="str">
-        <x:v>矩形</x:v>
-      </x:c>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="4" t="str">
-        <x:v>8,28</x:v>
-      </x:c>
-      <x:c r="J13" s="3" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
-      <x:c r="K13" s="3" t="str">
-        <x:v>直线</x:v>
-      </x:c>
-      <x:c r="L13" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="3" t="n">
-        <x:v>1150</x:v>
-      </x:c>
-      <x:c r="O13" s="16" t="n">
+      <x:c r="H20" s="64"/>
+      <x:c r="I20" s="64" t="str">
+        <x:v>20,47</x:v>
+      </x:c>
+      <x:c r="J20" s="63" t="str">
+        <x:v>0.5,0</x:v>
+      </x:c>
+      <x:c r="K20" s="63" t="str">
+        <x:v>跟踪</x:v>
+      </x:c>
+      <x:c r="L20" s="65" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M20" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N20" s="63" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="O20" s="63" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="P20" s="63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q20" s="63" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="R20" s="63" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="S20" s="63" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="T20" s="63" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="P13" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q13" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R13" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S13" s="16" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="T13"/>
-    </x:row>
-    <x:row r="14" ht="17.25">
-      <x:c r="A14" s="3"/>
-      <x:c r="B14" s="3" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C14" s="3" t="str">
-        <x:v>player_straight_short_shuttle</x:v>
-      </x:c>
-      <x:c r="D14" s="3" t="str">
-        <x:v>短梭形光弹，适合密集连续射击</x:v>
-      </x:c>
-      <x:c r="E14" s="3" t="str">
-        <x:v>图片</x:v>
-      </x:c>
-      <x:c r="F14" s="3" t="str">
-        <x:v>bullet/self/bullet_straight_light_short_shuttle</x:v>
-      </x:c>
-      <x:c r="G14" s="3" t="str">
-        <x:v>矩形</x:v>
-      </x:c>
-      <x:c r="H14" s="4"/>
-      <x:c r="I14" s="4" t="str">
-        <x:v>14,36</x:v>
-      </x:c>
-      <x:c r="J14" s="3" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
-      <x:c r="K14" s="3" t="str">
-        <x:v>直线</x:v>
-      </x:c>
-      <x:c r="L14" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M14" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="3" t="n">
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="O14" s="16" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="P14" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q14" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R14" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S14" s="16" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="T14"/>
-    </x:row>
-    <x:row r="15" ht="17.25">
-      <x:c r="A15" s="3"/>
-      <x:c r="B15" s="3" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C15" s="3" t="str">
-        <x:v>player_straight_twin_core</x:v>
-      </x:c>
-      <x:c r="D15" s="3" t="str">
-        <x:v>双核心光弹，适合强化型直线火力</x:v>
-      </x:c>
-      <x:c r="E15" s="3" t="str">
-        <x:v>图片</x:v>
-      </x:c>
-      <x:c r="F15" s="3" t="str">
-        <x:v>bullet/self/bullet_straight_light_twin_core</x:v>
-      </x:c>
-      <x:c r="G15" s="3" t="str">
-        <x:v>矩形</x:v>
-      </x:c>
-      <x:c r="H15" s="4"/>
-      <x:c r="I15" s="4" t="str">
-        <x:v>14,42</x:v>
-      </x:c>
-      <x:c r="J15" s="3" t="str">
-        <x:v>0.5,0.5</x:v>
-      </x:c>
-      <x:c r="K15" s="3" t="str">
-        <x:v>直线</x:v>
-      </x:c>
-      <x:c r="L15" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M15" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="3" t="n">
-        <x:v>950</x:v>
-      </x:c>
-      <x:c r="O15" s="16" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="P15" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q15" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R15" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S15" s="16" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="T15"/>
-    </x:row>
-    <x:row r="16" ht="17.25">
-      <x:c r="A16" s="3"/>
-      <x:c r="B16" s="3" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C16" s="3" t="str">
-        <x:v>player_tracking_dart</x:v>
-      </x:c>
-      <x:c r="D16" s="3" t="str">
-        <x:v>带稳定翼的轻型追踪飞镖</x:v>
-      </x:c>
-      <x:c r="E16" s="3" t="str">
-        <x:v>图片</x:v>
-      </x:c>
-      <x:c r="F16" s="3" t="str">
-        <x:v>bullet/self/bullet_tracking_dart</x:v>
-      </x:c>
-      <x:c r="G16" s="3" t="str">
-        <x:v>矩形</x:v>
-      </x:c>
-      <x:c r="H16" s="4"/>
-      <x:c r="I16" s="4" t="str">
-        <x:v>29,27</x:v>
-      </x:c>
-      <x:c r="J16" s="3" t="str">
-        <x:v>0.5,0</x:v>
-      </x:c>
-      <x:c r="K16" s="3" t="str">
-        <x:v>跟踪</x:v>
-      </x:c>
-      <x:c r="L16" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M16" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="3" t="n">
-        <x:v>560</x:v>
-      </x:c>
-      <x:c r="O16" s="16" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="P16" s="16" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q16" s="16" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="R16" s="16" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="S16" s="16" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="T16"/>
-    </x:row>
-    <x:row r="17" ht="17.25">
-      <x:c r="A17" s="3"/>
-      <x:c r="B17" s="3" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C17" s="3" t="str">
-        <x:v>player_tracking_micro</x:v>
-      </x:c>
-      <x:c r="D17" s="3" t="str">
-        <x:v>小型高速追踪弹，转向较灵活</x:v>
-      </x:c>
-      <x:c r="E17" s="3" t="str">
-        <x:v>图片</x:v>
-      </x:c>
-      <x:c r="F17" s="3" t="str">
-        <x:v>bullet/self/bullet_tracking_micro</x:v>
-      </x:c>
-      <x:c r="G17" s="3" t="str">
-        <x:v>矩形</x:v>
-      </x:c>
-      <x:c r="H17" s="4"/>
-      <x:c r="I17" s="4" t="str">
-        <x:v>7,16</x:v>
-      </x:c>
-      <x:c r="J17" s="3" t="str">
-        <x:v>0.5,0</x:v>
-      </x:c>
-      <x:c r="K17" s="3" t="str">
-        <x:v>跟踪</x:v>
-      </x:c>
-      <x:c r="L17" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M17" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="3" t="n">
-        <x:v>650</x:v>
-      </x:c>
-      <x:c r="O17" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="P17" s="16" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q17" s="16" t="n">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="R17" s="16" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="S17" s="16" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="T17"/>
-    </x:row>
-    <x:row r="18" ht="17.25">
-      <x:c r="A18" s="3"/>
-      <x:c r="B18" s="3" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C18" s="3" t="str">
-        <x:v>player_tracking_missile_standard</x:v>
-      </x:c>
-      <x:c r="D18" s="3" t="str">
-        <x:v>标准制式追踪导弹</x:v>
-      </x:c>
-      <x:c r="E18" s="3" t="str">
-        <x:v>图片</x:v>
-      </x:c>
-      <x:c r="F18" s="3" t="str">
-        <x:v>bullet/self/bullet_tracking_missile_standard</x:v>
-      </x:c>
-      <x:c r="G18" s="3" t="str">
-        <x:v>矩形</x:v>
-      </x:c>
-      <x:c r="H18" s="4"/>
-      <x:c r="I18" s="4" t="str">
-        <x:v>17,34</x:v>
-      </x:c>
-      <x:c r="J18" s="3" t="str">
-        <x:v>0.5,0</x:v>
-      </x:c>
-      <x:c r="K18" s="3" t="str">
-        <x:v>跟踪</x:v>
-      </x:c>
-      <x:c r="L18" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M18" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="3" t="n">
-        <x:v>520</x:v>
-      </x:c>
-      <x:c r="O18" s="16" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="P18" s="16" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q18" s="16" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="R18" s="16" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="S18" s="16" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="T18"/>
-    </x:row>
-    <x:row r="19" ht="17.25">
-      <x:c r="A19" s="3"/>
-      <x:c r="B19" s="3" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="3" t="str">
-        <x:v>player_tracking_torpedo_deep_sea</x:v>
-      </x:c>
-      <x:c r="D19" s="3" t="str">
-        <x:v>大型圆形深海鱼雷，缓慢但伤害较高</x:v>
-      </x:c>
-      <x:c r="E19" s="3" t="str">
-        <x:v>图片</x:v>
-      </x:c>
-      <x:c r="F19" s="3" t="str">
-        <x:v>bullet/self/bullet_tracking_torpedo_deep_sea</x:v>
-      </x:c>
-      <x:c r="G19" s="3" t="str">
-        <x:v>圆形</x:v>
-      </x:c>
-      <x:c r="H19" s="4" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="I19" s="4"/>
-      <x:c r="J19" s="3"/>
-      <x:c r="K19" s="3" t="str">
-        <x:v>跟踪</x:v>
-      </x:c>
-      <x:c r="L19" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M19" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="3" t="n">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="O19" s="16" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="P19" s="16" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q19" s="16" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="R19" s="16" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="S19" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="T19"/>
-    </x:row>
-    <x:row r="20" ht="17.25">
-      <x:c r="A20" s="3"/>
-      <x:c r="B20" s="3" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C20" s="3" t="str">
-        <x:v>player_tracking_torpedo_heavy</x:v>
-      </x:c>
-      <x:c r="D20" s="3" t="str">
-        <x:v>重型鱼雷，速度较慢且威力较高</x:v>
-      </x:c>
-      <x:c r="E20" s="3" t="str">
-        <x:v>图片</x:v>
-      </x:c>
-      <x:c r="F20" s="3" t="str">
-        <x:v>bullet/self/bullet_tracking_torpedo_heavy</x:v>
-      </x:c>
-      <x:c r="G20" s="3" t="str">
-        <x:v>矩形</x:v>
-      </x:c>
-      <x:c r="H20" s="4"/>
-      <x:c r="I20" s="4" t="str">
-        <x:v>20,47</x:v>
-      </x:c>
-      <x:c r="J20" s="3" t="str">
-        <x:v>0.5,0</x:v>
-      </x:c>
-      <x:c r="K20" s="3" t="str">
-        <x:v>跟踪</x:v>
-      </x:c>
-      <x:c r="L20" s="5" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M20" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="3" t="n">
-        <x:v>420</x:v>
-      </x:c>
-      <x:c r="O20" s="16" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="P20" s="16" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q20" s="16" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="R20" s="16" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="S20" s="16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="T20"/>
     </x:row>
     <x:row r="21" ht="17.25">
       <x:c r="A21"/>
@@ -2377,9 +2651,9 @@
   <x:mergeCells>
     <x:mergeCell ref="G4:J4"/>
     <x:mergeCell ref="G5:J5"/>
-    <x:mergeCell ref="E1:R1"/>
-    <x:mergeCell ref="E2:R2"/>
-    <x:mergeCell ref="E3:R3"/>
+    <x:mergeCell ref="E1:S1"/>
+    <x:mergeCell ref="E2:S2"/>
+    <x:mergeCell ref="E3:S3"/>
   </x:mergeCells>
   <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="E7:E200">
@@ -2396,6 +2670,6 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11e970351ce143dc"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc025028e7034424f"/>
 </x:worksheet>
 </file>
--- a/RaidenDemo/文档/配置表/BulletResource.xlsx
+++ b/RaidenDemo/文档/配置表/BulletResource.xlsx
@@ -1120,7 +1120,21 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="19">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1314,25 +1328,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="totalRow" dxfId="6"/>
+      <tableStyleElement type="firstColumn" dxfId="5"/>
+      <tableStyleElement type="lastColumn" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
+      <tableStyleElement type="pageFieldValues" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1550,7 +1564,7 @@
     <col min="9" max="9" width="13.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="10.75" style="1" customWidth="1"/>
     <col min="11" max="11" width="14" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="18.625" style="1" customWidth="1"/>
     <col min="13" max="13" width="12.875" style="1" customWidth="1"/>
     <col min="14" max="14" width="8.875" style="1" customWidth="1"/>
     <col min="15" max="15" width="8" style="1" customWidth="1"/>
@@ -1790,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="6">
-        <v>3150</v>
+        <v>2800</v>
       </c>
       <c r="O5" s="6">
         <v>10</v>
@@ -2112,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K13" s="6">
         <v>5</v>
@@ -2124,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="6">
-        <v>3150</v>
+        <v>2800</v>
       </c>
       <c r="O13" s="6">
         <v>10</v>
@@ -2155,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K14" s="6">
         <v>5</v>
@@ -2167,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="6">
-        <v>3150</v>
+        <v>2800</v>
       </c>
       <c r="O14" s="6">
         <v>10</v>
@@ -2198,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K15" s="6">
         <v>5</v>
@@ -2210,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="6">
-        <v>3150</v>
+        <v>2800</v>
       </c>
       <c r="O15" s="6">
         <v>10</v>
@@ -2241,7 +2255,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K16" s="6">
         <v>5</v>
@@ -2253,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="6">
-        <v>3150</v>
+        <v>2800</v>
       </c>
       <c r="O16" s="6">
         <v>10</v>
@@ -2284,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K17" s="6">
         <v>5</v>
@@ -2296,7 +2310,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="6">
-        <v>3150</v>
+        <v>2800</v>
       </c>
       <c r="O17" s="6">
         <v>10</v>
@@ -2327,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K18" s="6">
         <v>5</v>
@@ -2339,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="6">
-        <v>3150</v>
+        <v>2800</v>
       </c>
       <c r="O18" s="6">
         <v>10</v>
@@ -2370,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K19" s="6">
         <v>5</v>
@@ -2382,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="6">
-        <v>3150</v>
+        <v>2800</v>
       </c>
       <c r="O19" s="6">
         <v>10</v>
@@ -2413,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K20" s="6">
         <v>5</v>
@@ -2425,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="6">
-        <v>3150</v>
+        <v>2800</v>
       </c>
       <c r="O20" s="6">
         <v>10</v>
@@ -2456,7 +2470,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K21" s="6">
         <v>5</v>
@@ -2468,7 +2482,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="6">
-        <v>3150</v>
+        <v>2800</v>
       </c>
       <c r="O21" s="6">
         <v>10</v>
@@ -2499,7 +2513,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K22" s="6">
         <v>5</v>
@@ -2511,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="6">
-        <v>3150</v>
+        <v>2800</v>
       </c>
       <c r="O22" s="6">
         <v>10</v>
@@ -2544,7 +2558,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="6">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="K23" s="6">
         <v>14</v>
@@ -2593,7 +2607,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K24" s="6">
         <v>3</v>
@@ -2642,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="J25" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K25" s="6">
         <v>8</v>
@@ -2691,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K26" s="6">
         <v>24</v>
@@ -2740,7 +2754,7 @@
         <v>1</v>
       </c>
       <c r="J27" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K27" s="6">
         <v>10</v>
@@ -2787,7 +2801,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K28" s="6">
         <v>5</v>
@@ -2994,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K33" s="6">
         <v>10</v>
@@ -3037,7 +3051,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K34" s="6">
         <v>10</v>
@@ -3080,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="J35" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K35" s="6">
         <v>10</v>
@@ -3123,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K36" s="6">
         <v>10</v>
@@ -3166,7 +3180,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K37" s="6">
         <v>10</v>
@@ -3209,7 +3223,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K38" s="6">
         <v>20</v>
@@ -3252,7 +3266,7 @@
         <v>1</v>
       </c>
       <c r="J39" s="6">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="K39" s="6">
         <v>10</v>
@@ -3273,6 +3287,14 @@
       <c r="Q39" s="6"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="L4:L1048576">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"直线"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"跟踪"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" sqref="L4:L39">
       <formula1>"直线,跟踪"</formula1>

--- a/RaidenDemo/文档/配置表/BulletResource.xlsx
+++ b/RaidenDemo/文档/配置表/BulletResource.xlsx
@@ -544,7 +544,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -584,6 +584,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF8D8D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -921,7 +927,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
@@ -945,16 +951,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="7">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
@@ -963,90 +969,90 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1065,6 +1071,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2122,10 +2131,10 @@
       <c r="H13" s="6">
         <v>1001</v>
       </c>
-      <c r="I13" s="6">
-        <v>1</v>
-      </c>
-      <c r="J13" s="6">
+      <c r="I13" s="8">
+        <v>1</v>
+      </c>
+      <c r="J13" s="8">
         <v>2001</v>
       </c>
       <c r="K13" s="6">
@@ -2165,11 +2174,11 @@
       <c r="H14" s="6">
         <v>1002</v>
       </c>
-      <c r="I14" s="6">
-        <v>1</v>
-      </c>
-      <c r="J14" s="6">
-        <v>2001</v>
+      <c r="I14" s="8">
+        <v>6</v>
+      </c>
+      <c r="J14" s="8">
+        <v>2015</v>
       </c>
       <c r="K14" s="6">
         <v>5</v>
@@ -2208,11 +2217,11 @@
       <c r="H15" s="6">
         <v>1003</v>
       </c>
-      <c r="I15" s="6">
-        <v>1</v>
-      </c>
-      <c r="J15" s="6">
-        <v>2001</v>
+      <c r="I15" s="8">
+        <v>9</v>
+      </c>
+      <c r="J15" s="8">
+        <v>2008</v>
       </c>
       <c r="K15" s="6">
         <v>5</v>
@@ -2251,11 +2260,11 @@
       <c r="H16" s="6">
         <v>1004</v>
       </c>
-      <c r="I16" s="6">
-        <v>1</v>
-      </c>
-      <c r="J16" s="6">
-        <v>2001</v>
+      <c r="I16" s="8">
+        <v>7</v>
+      </c>
+      <c r="J16" s="8">
+        <v>2010</v>
       </c>
       <c r="K16" s="6">
         <v>5</v>
@@ -2294,11 +2303,11 @@
       <c r="H17" s="6">
         <v>1005</v>
       </c>
-      <c r="I17" s="6">
-        <v>1</v>
-      </c>
-      <c r="J17" s="6">
-        <v>2001</v>
+      <c r="I17" s="8">
+        <v>6</v>
+      </c>
+      <c r="J17" s="8">
+        <v>2004</v>
       </c>
       <c r="K17" s="6">
         <v>5</v>
@@ -2337,11 +2346,11 @@
       <c r="H18" s="6">
         <v>1006</v>
       </c>
-      <c r="I18" s="6">
-        <v>1</v>
-      </c>
-      <c r="J18" s="6">
-        <v>2001</v>
+      <c r="I18" s="8">
+        <v>5</v>
+      </c>
+      <c r="J18" s="8">
+        <v>2005</v>
       </c>
       <c r="K18" s="6">
         <v>5</v>
@@ -2380,11 +2389,11 @@
       <c r="H19" s="6">
         <v>1007</v>
       </c>
-      <c r="I19" s="6">
-        <v>1</v>
-      </c>
-      <c r="J19" s="6">
-        <v>2001</v>
+      <c r="I19" s="8">
+        <v>7</v>
+      </c>
+      <c r="J19" s="8">
+        <v>2013</v>
       </c>
       <c r="K19" s="6">
         <v>5</v>
@@ -2423,11 +2432,11 @@
       <c r="H20" s="6">
         <v>1008</v>
       </c>
-      <c r="I20" s="6">
-        <v>1</v>
-      </c>
-      <c r="J20" s="6">
-        <v>2001</v>
+      <c r="I20" s="8">
+        <v>7</v>
+      </c>
+      <c r="J20" s="8">
+        <v>2012</v>
       </c>
       <c r="K20" s="6">
         <v>5</v>
@@ -2466,11 +2475,11 @@
       <c r="H21" s="6">
         <v>1051</v>
       </c>
-      <c r="I21" s="6">
-        <v>1</v>
-      </c>
-      <c r="J21" s="6">
-        <v>2001</v>
+      <c r="I21" s="8">
+        <v>8</v>
+      </c>
+      <c r="J21" s="8">
+        <v>2009</v>
       </c>
       <c r="K21" s="6">
         <v>5</v>
@@ -2509,11 +2518,11 @@
       <c r="H22" s="6">
         <v>1201</v>
       </c>
-      <c r="I22" s="6">
-        <v>1</v>
-      </c>
-      <c r="J22" s="6">
-        <v>2001</v>
+      <c r="I22" s="8">
+        <v>10</v>
+      </c>
+      <c r="J22" s="8">
+        <v>1007</v>
       </c>
       <c r="K22" s="6">
         <v>5</v>
@@ -2800,8 +2809,8 @@
       <c r="I28" s="6">
         <v>1</v>
       </c>
-      <c r="J28" s="6">
-        <v>2001</v>
+      <c r="J28" s="8">
+        <v>2014</v>
       </c>
       <c r="K28" s="6">
         <v>5</v>
@@ -3007,8 +3016,8 @@
       <c r="I33" s="6">
         <v>1</v>
       </c>
-      <c r="J33" s="6">
-        <v>2001</v>
+      <c r="J33" s="8">
+        <v>2014</v>
       </c>
       <c r="K33" s="6">
         <v>10</v>
@@ -3050,8 +3059,8 @@
       <c r="I34" s="6">
         <v>1</v>
       </c>
-      <c r="J34" s="6">
-        <v>2001</v>
+      <c r="J34" s="8">
+        <v>2014</v>
       </c>
       <c r="K34" s="6">
         <v>10</v>
@@ -3093,8 +3102,8 @@
       <c r="I35" s="6">
         <v>1</v>
       </c>
-      <c r="J35" s="6">
-        <v>2001</v>
+      <c r="J35" s="8">
+        <v>2014</v>
       </c>
       <c r="K35" s="6">
         <v>10</v>
@@ -3136,8 +3145,8 @@
       <c r="I36" s="6">
         <v>1</v>
       </c>
-      <c r="J36" s="6">
-        <v>2001</v>
+      <c r="J36" s="8">
+        <v>2014</v>
       </c>
       <c r="K36" s="6">
         <v>10</v>
@@ -3179,8 +3188,8 @@
       <c r="I37" s="6">
         <v>1</v>
       </c>
-      <c r="J37" s="6">
-        <v>2001</v>
+      <c r="J37" s="8">
+        <v>2014</v>
       </c>
       <c r="K37" s="6">
         <v>10</v>
@@ -3222,8 +3231,8 @@
       <c r="I38" s="6">
         <v>1</v>
       </c>
-      <c r="J38" s="6">
-        <v>2001</v>
+      <c r="J38" s="8">
+        <v>2014</v>
       </c>
       <c r="K38" s="6">
         <v>20</v>
@@ -3265,8 +3274,8 @@
       <c r="I39" s="6">
         <v>1</v>
       </c>
-      <c r="J39" s="6">
-        <v>2001</v>
+      <c r="J39" s="8">
+        <v>2014</v>
       </c>
       <c r="K39" s="6">
         <v>10</v>

--- a/RaidenDemo/文档/配置表/BulletResource.xlsx
+++ b/RaidenDemo/文档/配置表/BulletResource.xlsx
@@ -544,7 +544,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -553,6 +553,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF000000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -565,25 +571,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8D8D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.25"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF8D8D"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -927,7 +939,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
@@ -951,16 +963,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="7">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
@@ -969,99 +981,97 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="38" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="49" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1076,6 +1086,13 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1561,1739 +1578,1748 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="35.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="36" style="1" customWidth="1"/>
-    <col min="5" max="6" width="8.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="46.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14" style="1" customWidth="1"/>
-    <col min="12" max="12" width="18.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="8" style="1" customWidth="1"/>
-    <col min="16" max="16" width="21.25" style="1" customWidth="1"/>
-    <col min="17" max="17" width="21.875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="13.75" style="1" customWidth="1"/>
+    <col min="1" max="2" width="10" style="2" customWidth="1"/>
+    <col min="3" max="3" width="35.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="36" style="2" customWidth="1"/>
+    <col min="5" max="6" width="8.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="46.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="8.875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="8" style="2" customWidth="1"/>
+    <col min="16" max="16" width="21.25" style="2" customWidth="1"/>
+    <col min="17" max="17" width="21.875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="13.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:17">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:17">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:17">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A4" s="4" t="s">
+    <row r="4" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6">
-        <v>1</v>
-      </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6">
+      <c r="H4" s="5"/>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="M4" s="6">
-        <v>0</v>
-      </c>
-      <c r="N4" s="6">
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
         <v>420</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="5">
         <v>12</v>
       </c>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A5" s="4" t="s">
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="11"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="5">
         <v>2</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6" t="s">
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6">
-        <v>1</v>
-      </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6">
+      <c r="H5" s="5"/>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5">
         <v>7</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="6">
-        <v>0</v>
-      </c>
-      <c r="N5" s="6">
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
         <v>2800</v>
       </c>
-      <c r="O5" s="6">
+      <c r="O5" s="5">
         <v>10</v>
       </c>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-    </row>
-    <row r="6" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A6" s="4" t="s">
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="11"/>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="5">
         <v>3</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6" t="s">
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6">
-        <v>1</v>
-      </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6">
+      <c r="H6" s="5"/>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5">
         <v>14</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="M6" s="6">
-        <v>0</v>
-      </c>
-      <c r="N6" s="6">
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
         <v>624</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="5">
         <v>10</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="5">
         <v>300</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="Q6" s="5">
         <v>180</v>
       </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A7" s="4" t="s">
+      <c r="R6" s="11"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="5">
         <v>4</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6">
-        <v>1</v>
-      </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6">
+      <c r="H7" s="5"/>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5">
         <v>6</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6">
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
         <v>1350</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="5">
         <v>10</v>
       </c>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-    </row>
-    <row r="8" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A8" s="4" t="s">
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="11"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A8" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="5">
         <v>5</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6" t="s">
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6">
-        <v>1</v>
-      </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6">
+      <c r="H8" s="5"/>
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5">
         <v>7</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="M8" s="6">
-        <v>0</v>
-      </c>
-      <c r="N8" s="6">
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
         <v>1200</v>
       </c>
-      <c r="O8" s="6">
+      <c r="O8" s="5">
         <v>18</v>
       </c>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-    </row>
-    <row r="9" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A9" s="4" t="s">
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="11"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A9" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="5">
         <v>6</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6" t="s">
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6">
-        <v>1</v>
-      </c>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6">
+      <c r="H9" s="5"/>
+      <c r="I9" s="5">
+        <v>1</v>
+      </c>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5">
         <v>9</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="M9" s="6">
-        <v>0</v>
-      </c>
-      <c r="N9" s="6">
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
         <v>2700</v>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="5">
         <v>14</v>
       </c>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A10" s="4" t="s">
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="11"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A10" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="5">
         <v>7</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6" t="s">
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6">
-        <v>1</v>
-      </c>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6">
+      <c r="H10" s="5"/>
+      <c r="I10" s="5">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="M10" s="6">
-        <v>0</v>
-      </c>
-      <c r="N10" s="6">
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
         <v>1725</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="5">
         <v>8</v>
       </c>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A11" s="4" t="s">
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="11"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A11" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="5">
         <v>8</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6" t="s">
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6">
-        <v>1</v>
-      </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6">
+      <c r="H11" s="5"/>
+      <c r="I11" s="5">
+        <v>1</v>
+      </c>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="M11" s="6">
-        <v>0</v>
-      </c>
-      <c r="N11" s="6">
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
         <v>1500</v>
       </c>
-      <c r="O11" s="6">
+      <c r="O11" s="5">
         <v>10</v>
       </c>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-    </row>
-    <row r="12" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A12" s="4" t="s">
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="11"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:18">
+      <c r="A12" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B12" s="5">
         <v>9</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6" t="s">
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6">
-        <v>1</v>
-      </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6">
+      <c r="H12" s="5"/>
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5">
         <v>7</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="M12" s="6">
-        <v>0</v>
-      </c>
-      <c r="N12" s="6">
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
         <v>1425</v>
       </c>
-      <c r="O12" s="6">
+      <c r="O12" s="5">
         <v>12</v>
       </c>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="11"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A13" s="4"/>
-      <c r="B13" s="6">
+      <c r="A13" s="6"/>
+      <c r="B13" s="7">
         <v>1001</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>1001</v>
       </c>
-      <c r="F13" s="6">
-        <v>1</v>
-      </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6">
+      <c r="F13" s="7">
+        <v>1</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7">
         <v>1001</v>
       </c>
-      <c r="I13" s="8">
-        <v>1</v>
-      </c>
-      <c r="J13" s="8">
+      <c r="I13" s="10">
+        <v>1</v>
+      </c>
+      <c r="J13" s="10">
         <v>2001</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="7">
         <v>5</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M13" s="6">
-        <v>0</v>
-      </c>
-      <c r="N13" s="6">
+      <c r="M13" s="7">
+        <v>0</v>
+      </c>
+      <c r="N13" s="7">
         <v>2800</v>
       </c>
-      <c r="O13" s="6">
+      <c r="O13" s="7">
         <v>10</v>
       </c>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A14" s="4"/>
-      <c r="B14" s="6">
+      <c r="A14" s="6"/>
+      <c r="B14" s="7">
         <v>1002</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6" t="s">
+      <c r="C14" s="7"/>
+      <c r="D14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>1001</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="7">
         <v>2</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6">
+      <c r="G14" s="7"/>
+      <c r="H14" s="7">
         <v>1002</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="10">
         <v>6</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="10">
         <v>2015</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="7">
         <v>5</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M14" s="6">
-        <v>0</v>
-      </c>
-      <c r="N14" s="6">
+      <c r="M14" s="7">
+        <v>0</v>
+      </c>
+      <c r="N14" s="7">
         <v>2800</v>
       </c>
-      <c r="O14" s="6">
+      <c r="O14" s="7">
         <v>10</v>
       </c>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A15" s="4"/>
-      <c r="B15" s="6">
+      <c r="A15" s="6"/>
+      <c r="B15" s="7">
         <v>1003</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6" t="s">
+      <c r="C15" s="7"/>
+      <c r="D15" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="7">
         <v>1003</v>
       </c>
-      <c r="F15" s="6">
-        <v>1</v>
-      </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6">
+      <c r="F15" s="7">
+        <v>1</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7">
         <v>1003</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="10">
         <v>9</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="10">
         <v>2008</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="7">
         <v>5</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M15" s="6">
-        <v>0</v>
-      </c>
-      <c r="N15" s="6">
+      <c r="M15" s="7">
+        <v>0</v>
+      </c>
+      <c r="N15" s="7">
+        <v>800</v>
+      </c>
+      <c r="O15" s="7">
+        <v>2</v>
+      </c>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+    </row>
+    <row r="16" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A16" s="6"/>
+      <c r="B16" s="7">
+        <v>1004</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1003</v>
+      </c>
+      <c r="F16" s="7">
+        <v>2</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7">
+        <v>1004</v>
+      </c>
+      <c r="I16" s="10">
+        <v>7</v>
+      </c>
+      <c r="J16" s="10">
+        <v>2010</v>
+      </c>
+      <c r="K16" s="7">
+        <v>5</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M16" s="7">
+        <v>0</v>
+      </c>
+      <c r="N16" s="7">
         <v>2800</v>
       </c>
-      <c r="O15" s="6">
+      <c r="O16" s="7">
         <v>10</v>
       </c>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-    </row>
-    <row r="16" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A16" s="4"/>
-      <c r="B16" s="6">
-        <v>1004</v>
-      </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="6">
-        <v>1003</v>
-      </c>
-      <c r="F16" s="6">
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7">
+        <v>1005</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1005</v>
+      </c>
+      <c r="F17" s="7">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7">
+        <v>1005</v>
+      </c>
+      <c r="I17" s="10">
+        <v>6</v>
+      </c>
+      <c r="J17" s="10">
+        <v>2004</v>
+      </c>
+      <c r="K17" s="7">
+        <v>5</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M17" s="7">
+        <v>0</v>
+      </c>
+      <c r="N17" s="7">
+        <v>2800</v>
+      </c>
+      <c r="O17" s="7">
+        <v>10</v>
+      </c>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A18" s="6"/>
+      <c r="B18" s="7">
+        <v>1006</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1005</v>
+      </c>
+      <c r="F18" s="7">
         <v>2</v>
       </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6">
-        <v>1004</v>
-      </c>
-      <c r="I16" s="8">
+      <c r="G18" s="7"/>
+      <c r="H18" s="7">
+        <v>1006</v>
+      </c>
+      <c r="I18" s="10">
+        <v>5</v>
+      </c>
+      <c r="J18" s="10">
+        <v>2005</v>
+      </c>
+      <c r="K18" s="7">
+        <v>5</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M18" s="7">
+        <v>0</v>
+      </c>
+      <c r="N18" s="7">
+        <v>2800</v>
+      </c>
+      <c r="O18" s="7">
+        <v>10</v>
+      </c>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A19" s="6"/>
+      <c r="B19" s="7">
+        <v>1007</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1007</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7">
+        <v>1007</v>
+      </c>
+      <c r="I19" s="10">
         <v>7</v>
       </c>
-      <c r="J16" s="8">
-        <v>2010</v>
-      </c>
-      <c r="K16" s="6">
+      <c r="J19" s="10">
+        <v>2013</v>
+      </c>
+      <c r="K19" s="7">
         <v>5</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="L19" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M16" s="6">
-        <v>0</v>
-      </c>
-      <c r="N16" s="6">
+      <c r="M19" s="7">
+        <v>0</v>
+      </c>
+      <c r="N19" s="7">
         <v>2800</v>
       </c>
-      <c r="O16" s="6">
+      <c r="O19" s="7">
         <v>10</v>
       </c>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-    </row>
-    <row r="17" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A17" s="4"/>
-      <c r="B17" s="6">
-        <v>1005</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1005</v>
-      </c>
-      <c r="F17" s="6">
-        <v>1</v>
-      </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6">
-        <v>1005</v>
-      </c>
-      <c r="I17" s="8">
-        <v>6</v>
-      </c>
-      <c r="J17" s="8">
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+    </row>
+    <row r="20" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7">
+        <v>1008</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1007</v>
+      </c>
+      <c r="F20" s="7">
+        <v>2</v>
+      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7">
+        <v>1008</v>
+      </c>
+      <c r="I20" s="10">
+        <v>7</v>
+      </c>
+      <c r="J20" s="10">
+        <v>2012</v>
+      </c>
+      <c r="K20" s="7">
+        <v>5</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M20" s="7">
+        <v>0</v>
+      </c>
+      <c r="N20" s="7">
+        <v>2800</v>
+      </c>
+      <c r="O20" s="7">
+        <v>10</v>
+      </c>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A21" s="6"/>
+      <c r="B21" s="7">
+        <v>1051</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1051</v>
+      </c>
+      <c r="F21" s="7">
+        <v>1</v>
+      </c>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7">
+        <v>1051</v>
+      </c>
+      <c r="I21" s="10">
+        <v>8</v>
+      </c>
+      <c r="J21" s="10">
+        <v>2009</v>
+      </c>
+      <c r="K21" s="7">
+        <v>5</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M21" s="7">
+        <v>0</v>
+      </c>
+      <c r="N21" s="7">
+        <v>2800</v>
+      </c>
+      <c r="O21" s="7">
+        <v>10</v>
+      </c>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7">
+        <v>1201</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1201</v>
+      </c>
+      <c r="F22" s="7">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7">
+        <v>1201</v>
+      </c>
+      <c r="I22" s="10">
+        <v>10</v>
+      </c>
+      <c r="J22" s="10">
+        <v>2001</v>
+      </c>
+      <c r="K22" s="7">
+        <v>5</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M22" s="7">
+        <v>0</v>
+      </c>
+      <c r="N22" s="7">
+        <v>800</v>
+      </c>
+      <c r="O22" s="7">
+        <v>1</v>
+      </c>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A23" s="6"/>
+      <c r="B23" s="7">
+        <v>2001</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="7">
+        <v>2001</v>
+      </c>
+      <c r="F23" s="7">
+        <v>1</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7">
+        <v>1</v>
+      </c>
+      <c r="J23" s="7">
+        <v>2001</v>
+      </c>
+      <c r="K23" s="7">
+        <v>14</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M23" s="7">
+        <v>0</v>
+      </c>
+      <c r="N23" s="7">
+        <v>560</v>
+      </c>
+      <c r="O23" s="7">
+        <v>14</v>
+      </c>
+      <c r="P23" s="7">
+        <v>300</v>
+      </c>
+      <c r="Q23" s="7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A24" s="6"/>
+      <c r="B24" s="7">
+        <v>2002</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2002</v>
+      </c>
+      <c r="F24" s="7">
+        <v>1</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7">
+        <v>1</v>
+      </c>
+      <c r="J24" s="7">
+        <v>2001</v>
+      </c>
+      <c r="K24" s="7">
+        <v>3</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M24" s="7">
+        <v>0</v>
+      </c>
+      <c r="N24" s="7">
+        <v>650</v>
+      </c>
+      <c r="O24" s="7">
+        <v>8</v>
+      </c>
+      <c r="P24" s="7">
+        <v>250</v>
+      </c>
+      <c r="Q24" s="7">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A25" s="6"/>
+      <c r="B25" s="7">
+        <v>2003</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="7">
+        <v>2003</v>
+      </c>
+      <c r="F25" s="7">
+        <v>1</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7">
+        <v>1</v>
+      </c>
+      <c r="J25" s="7">
+        <v>2001</v>
+      </c>
+      <c r="K25" s="7">
+        <v>8</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M25" s="7">
+        <v>0</v>
+      </c>
+      <c r="N25" s="7">
+        <v>400</v>
+      </c>
+      <c r="O25" s="7">
+        <v>16</v>
+      </c>
+      <c r="P25" s="7">
+        <v>300</v>
+      </c>
+      <c r="Q25" s="7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A26" s="6"/>
+      <c r="B26" s="7">
         <v>2004</v>
       </c>
-      <c r="K17" s="6">
+      <c r="C26" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2004</v>
+      </c>
+      <c r="F26" s="7">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7">
+        <v>1</v>
+      </c>
+      <c r="J26" s="7">
+        <v>2001</v>
+      </c>
+      <c r="K26" s="7">
+        <v>24</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M26" s="7">
+        <v>0</v>
+      </c>
+      <c r="N26" s="7">
+        <v>360</v>
+      </c>
+      <c r="O26" s="7">
+        <v>28</v>
+      </c>
+      <c r="P26" s="7">
+        <v>450</v>
+      </c>
+      <c r="Q26" s="7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A27" s="6"/>
+      <c r="B27" s="7">
+        <v>2005</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2005</v>
+      </c>
+      <c r="F27" s="7">
+        <v>1</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7">
+        <v>1</v>
+      </c>
+      <c r="J27" s="7">
+        <v>2001</v>
+      </c>
+      <c r="K27" s="7">
+        <v>10</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M27" s="7">
+        <v>10</v>
+      </c>
+      <c r="N27" s="7">
+        <v>420</v>
+      </c>
+      <c r="O27" s="7">
+        <v>24</v>
+      </c>
+      <c r="P27" s="7">
+        <v>400</v>
+      </c>
+      <c r="Q27" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A28" s="8"/>
+      <c r="B28" s="7">
+        <v>11001</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="7">
+        <v>11001</v>
+      </c>
+      <c r="F28" s="7">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7">
+        <v>1</v>
+      </c>
+      <c r="J28" s="10">
+        <v>2014</v>
+      </c>
+      <c r="K28" s="7">
         <v>5</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L28" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M17" s="6">
-        <v>0</v>
-      </c>
-      <c r="N17" s="6">
-        <v>2800</v>
-      </c>
-      <c r="O17" s="6">
+      <c r="M28" s="7">
+        <v>0</v>
+      </c>
+      <c r="N28" s="7">
+        <v>420</v>
+      </c>
+      <c r="O28" s="7">
+        <v>12</v>
+      </c>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A29" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="9">
+        <v>11002</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" s="7">
+        <v>11002</v>
+      </c>
+      <c r="F29" s="7">
+        <v>1</v>
+      </c>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7">
+        <v>1</v>
+      </c>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7">
+        <v>5</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M29" s="7">
+        <v>0</v>
+      </c>
+      <c r="N29" s="7">
+        <v>420</v>
+      </c>
+      <c r="O29" s="7">
+        <v>12</v>
+      </c>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A30" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="9">
+        <v>11003</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E30" s="7">
+        <v>11003</v>
+      </c>
+      <c r="F30" s="7">
+        <v>1</v>
+      </c>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7">
+        <v>1</v>
+      </c>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7">
+        <v>5</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M30" s="7">
+        <v>0</v>
+      </c>
+      <c r="N30" s="7">
+        <v>420</v>
+      </c>
+      <c r="O30" s="7">
+        <v>12</v>
+      </c>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+    </row>
+    <row r="31" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A31" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="9">
+        <v>11004</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" s="7">
+        <v>11004</v>
+      </c>
+      <c r="F31" s="7">
+        <v>1</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7">
+        <v>1</v>
+      </c>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7">
+        <v>5</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M31" s="7">
+        <v>0</v>
+      </c>
+      <c r="N31" s="7">
+        <v>420</v>
+      </c>
+      <c r="O31" s="7">
+        <v>12</v>
+      </c>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+    </row>
+    <row r="32" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A32" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="9">
+        <v>11005</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="7">
+        <v>11005</v>
+      </c>
+      <c r="F32" s="7">
+        <v>1</v>
+      </c>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7">
+        <v>1</v>
+      </c>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7">
+        <v>5</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M32" s="7">
+        <v>0</v>
+      </c>
+      <c r="N32" s="7">
+        <v>420</v>
+      </c>
+      <c r="O32" s="7">
+        <v>12</v>
+      </c>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A33" s="8"/>
+      <c r="B33" s="7">
+        <v>12001</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" s="7">
+        <v>12001</v>
+      </c>
+      <c r="F33" s="7">
+        <v>1</v>
+      </c>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7">
+        <v>1801</v>
+      </c>
+      <c r="I33" s="7">
+        <v>1</v>
+      </c>
+      <c r="J33" s="10">
+        <v>2014</v>
+      </c>
+      <c r="K33" s="7">
         <v>10</v>
       </c>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-    </row>
-    <row r="18" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A18" s="4"/>
-      <c r="B18" s="6">
-        <v>1006</v>
-      </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1005</v>
-      </c>
-      <c r="F18" s="6">
-        <v>2</v>
-      </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6">
-        <v>1006</v>
-      </c>
-      <c r="I18" s="8">
-        <v>5</v>
-      </c>
-      <c r="J18" s="8">
-        <v>2005</v>
-      </c>
-      <c r="K18" s="6">
-        <v>5</v>
-      </c>
-      <c r="L18" s="6" t="s">
+      <c r="L33" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M18" s="6">
-        <v>0</v>
-      </c>
-      <c r="N18" s="6">
-        <v>2800</v>
-      </c>
-      <c r="O18" s="6">
+      <c r="M33" s="7">
+        <v>0</v>
+      </c>
+      <c r="N33" s="7">
+        <v>420</v>
+      </c>
+      <c r="O33" s="7">
         <v>10</v>
       </c>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-    </row>
-    <row r="19" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A19" s="4"/>
-      <c r="B19" s="6">
-        <v>1007</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19" s="6">
-        <v>1007</v>
-      </c>
-      <c r="F19" s="6">
-        <v>1</v>
-      </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6">
-        <v>1007</v>
-      </c>
-      <c r="I19" s="8">
-        <v>7</v>
-      </c>
-      <c r="J19" s="8">
-        <v>2013</v>
-      </c>
-      <c r="K19" s="6">
-        <v>5</v>
-      </c>
-      <c r="L19" s="6" t="s">
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A34" s="8"/>
+      <c r="B34" s="7">
+        <v>12002</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="7">
+        <v>12002</v>
+      </c>
+      <c r="F34" s="7">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7">
+        <v>1802</v>
+      </c>
+      <c r="I34" s="7">
+        <v>1</v>
+      </c>
+      <c r="J34" s="10">
+        <v>2014</v>
+      </c>
+      <c r="K34" s="7">
+        <v>10</v>
+      </c>
+      <c r="L34" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M19" s="6">
-        <v>0</v>
-      </c>
-      <c r="N19" s="6">
-        <v>2800</v>
-      </c>
-      <c r="O19" s="6">
+      <c r="M34" s="7">
+        <v>0</v>
+      </c>
+      <c r="N34" s="7">
+        <v>420</v>
+      </c>
+      <c r="O34" s="7">
         <v>10</v>
       </c>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-    </row>
-    <row r="20" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A20" s="4"/>
-      <c r="B20" s="6">
-        <v>1008</v>
-      </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="6">
-        <v>1007</v>
-      </c>
-      <c r="F20" s="6">
-        <v>2</v>
-      </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6">
-        <v>1008</v>
-      </c>
-      <c r="I20" s="8">
-        <v>7</v>
-      </c>
-      <c r="J20" s="8">
-        <v>2012</v>
-      </c>
-      <c r="K20" s="6">
-        <v>5</v>
-      </c>
-      <c r="L20" s="6" t="s">
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A35" s="8"/>
+      <c r="B35" s="7">
+        <v>12003</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E35" s="7">
+        <v>12003</v>
+      </c>
+      <c r="F35" s="7">
+        <v>1</v>
+      </c>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7">
+        <v>1803</v>
+      </c>
+      <c r="I35" s="7">
+        <v>1</v>
+      </c>
+      <c r="J35" s="10">
+        <v>2014</v>
+      </c>
+      <c r="K35" s="7">
+        <v>10</v>
+      </c>
+      <c r="L35" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M20" s="6">
-        <v>0</v>
-      </c>
-      <c r="N20" s="6">
-        <v>2800</v>
-      </c>
-      <c r="O20" s="6">
+      <c r="M35" s="7">
+        <v>0</v>
+      </c>
+      <c r="N35" s="7">
+        <v>420</v>
+      </c>
+      <c r="O35" s="7">
         <v>10</v>
       </c>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-    </row>
-    <row r="21" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A21" s="4"/>
-      <c r="B21" s="6">
-        <v>1051</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1051</v>
-      </c>
-      <c r="F21" s="6">
-        <v>1</v>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6">
-        <v>1051</v>
-      </c>
-      <c r="I21" s="8">
-        <v>8</v>
-      </c>
-      <c r="J21" s="8">
-        <v>2009</v>
-      </c>
-      <c r="K21" s="6">
-        <v>5</v>
-      </c>
-      <c r="L21" s="6" t="s">
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A36" s="8"/>
+      <c r="B36" s="7">
+        <v>12004</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" s="7">
+        <v>12004</v>
+      </c>
+      <c r="F36" s="7">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7">
+        <v>1804</v>
+      </c>
+      <c r="I36" s="7">
+        <v>1</v>
+      </c>
+      <c r="J36" s="10">
+        <v>2014</v>
+      </c>
+      <c r="K36" s="7">
+        <v>10</v>
+      </c>
+      <c r="L36" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M21" s="6">
-        <v>0</v>
-      </c>
-      <c r="N21" s="6">
-        <v>2800</v>
-      </c>
-      <c r="O21" s="6">
+      <c r="M36" s="7">
+        <v>0</v>
+      </c>
+      <c r="N36" s="7">
+        <v>420</v>
+      </c>
+      <c r="O36" s="7">
         <v>10</v>
       </c>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
-    </row>
-    <row r="22" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A22" s="4"/>
-      <c r="B22" s="6">
-        <v>1201</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" s="6">
-        <v>1201</v>
-      </c>
-      <c r="F22" s="6">
-        <v>1</v>
-      </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6">
-        <v>1201</v>
-      </c>
-      <c r="I22" s="8">
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A37" s="8"/>
+      <c r="B37" s="7">
+        <v>12005</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E37" s="7">
+        <v>12005</v>
+      </c>
+      <c r="F37" s="7">
+        <v>1</v>
+      </c>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7">
+        <v>1805</v>
+      </c>
+      <c r="I37" s="7">
+        <v>1</v>
+      </c>
+      <c r="J37" s="10">
+        <v>2014</v>
+      </c>
+      <c r="K37" s="7">
         <v>10</v>
       </c>
-      <c r="J22" s="8">
-        <v>1007</v>
-      </c>
-      <c r="K22" s="6">
-        <v>5</v>
-      </c>
-      <c r="L22" s="6" t="s">
+      <c r="L37" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M22" s="6">
-        <v>0</v>
-      </c>
-      <c r="N22" s="6">
-        <v>2800</v>
-      </c>
-      <c r="O22" s="6">
+      <c r="M37" s="7">
+        <v>0</v>
+      </c>
+      <c r="N37" s="7">
+        <v>420</v>
+      </c>
+      <c r="O37" s="7">
         <v>10</v>
       </c>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-    </row>
-    <row r="23" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A23" s="4"/>
-      <c r="B23" s="6">
-        <v>2001</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E23" s="6">
-        <v>2001</v>
-      </c>
-      <c r="F23" s="6">
-        <v>1</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6">
-        <v>1</v>
-      </c>
-      <c r="J23" s="6">
-        <v>2001</v>
-      </c>
-      <c r="K23" s="6">
-        <v>14</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M23" s="6">
-        <v>0</v>
-      </c>
-      <c r="N23" s="6">
-        <v>560</v>
-      </c>
-      <c r="O23" s="6">
-        <v>14</v>
-      </c>
-      <c r="P23" s="6">
-        <v>300</v>
-      </c>
-      <c r="Q23" s="6">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A24" s="4"/>
-      <c r="B24" s="6">
-        <v>2002</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E24" s="6">
-        <v>2002</v>
-      </c>
-      <c r="F24" s="6">
-        <v>1</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6">
-        <v>1</v>
-      </c>
-      <c r="J24" s="6">
-        <v>2001</v>
-      </c>
-      <c r="K24" s="6">
-        <v>3</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M24" s="6">
-        <v>0</v>
-      </c>
-      <c r="N24" s="6">
-        <v>650</v>
-      </c>
-      <c r="O24" s="6">
-        <v>8</v>
-      </c>
-      <c r="P24" s="6">
-        <v>250</v>
-      </c>
-      <c r="Q24" s="6">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A25" s="4"/>
-      <c r="B25" s="6">
-        <v>2003</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E25" s="6">
-        <v>2003</v>
-      </c>
-      <c r="F25" s="6">
-        <v>1</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6">
-        <v>1</v>
-      </c>
-      <c r="J25" s="6">
-        <v>2001</v>
-      </c>
-      <c r="K25" s="6">
-        <v>8</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M25" s="6">
-        <v>0</v>
-      </c>
-      <c r="N25" s="6">
-        <v>520</v>
-      </c>
-      <c r="O25" s="6">
-        <v>16</v>
-      </c>
-      <c r="P25" s="6">
-        <v>300</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A26" s="4"/>
-      <c r="B26" s="6">
-        <v>2004</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="6">
-        <v>2004</v>
-      </c>
-      <c r="F26" s="6">
-        <v>1</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6">
-        <v>1</v>
-      </c>
-      <c r="J26" s="6">
-        <v>2001</v>
-      </c>
-      <c r="K26" s="6">
-        <v>24</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M26" s="6">
-        <v>0</v>
-      </c>
-      <c r="N26" s="6">
-        <v>360</v>
-      </c>
-      <c r="O26" s="6">
-        <v>28</v>
-      </c>
-      <c r="P26" s="6">
-        <v>450</v>
-      </c>
-      <c r="Q26" s="6">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A27" s="4"/>
-      <c r="B27" s="6">
-        <v>2005</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E27" s="6">
-        <v>2005</v>
-      </c>
-      <c r="F27" s="6">
-        <v>1</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6">
-        <v>1</v>
-      </c>
-      <c r="J27" s="6">
-        <v>2001</v>
-      </c>
-      <c r="K27" s="6">
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A38" s="8"/>
+      <c r="B38" s="7">
+        <v>12006</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E38" s="7">
+        <v>12006</v>
+      </c>
+      <c r="F38" s="7">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7">
+        <v>1806</v>
+      </c>
+      <c r="I38" s="7">
+        <v>1</v>
+      </c>
+      <c r="J38" s="10">
+        <v>2014</v>
+      </c>
+      <c r="K38" s="7">
+        <v>20</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M38" s="7">
+        <v>0</v>
+      </c>
+      <c r="N38" s="7">
+        <v>320</v>
+      </c>
+      <c r="O38" s="7">
         <v>10</v>
       </c>
-      <c r="L27" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M27" s="6">
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" spans="1:17">
+      <c r="A39" s="8"/>
+      <c r="B39" s="7">
+        <v>12007</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E39" s="7">
+        <v>12007</v>
+      </c>
+      <c r="F39" s="7">
+        <v>1</v>
+      </c>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7">
+        <v>1807</v>
+      </c>
+      <c r="I39" s="7">
+        <v>1</v>
+      </c>
+      <c r="J39" s="10">
+        <v>2014</v>
+      </c>
+      <c r="K39" s="7">
         <v>10</v>
       </c>
-      <c r="N27" s="6">
+      <c r="L39" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M39" s="7">
+        <v>0</v>
+      </c>
+      <c r="N39" s="7">
         <v>420</v>
       </c>
-      <c r="O27" s="6">
-        <v>24</v>
-      </c>
-      <c r="P27" s="6">
-        <v>400</v>
-      </c>
-      <c r="Q27" s="6">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A28" s="7"/>
-      <c r="B28" s="6">
-        <v>11001</v>
-      </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="6">
-        <v>11001</v>
-      </c>
-      <c r="F28" s="6">
-        <v>1</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6">
-        <v>1</v>
-      </c>
-      <c r="J28" s="8">
-        <v>2014</v>
-      </c>
-      <c r="K28" s="6">
-        <v>5</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M28" s="6">
-        <v>0</v>
-      </c>
-      <c r="N28" s="6">
-        <v>420</v>
-      </c>
-      <c r="O28" s="6">
-        <v>12</v>
-      </c>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-    </row>
-    <row r="29" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A29" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" s="5">
-        <v>11002</v>
-      </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29" s="6">
-        <v>11002</v>
-      </c>
-      <c r="F29" s="6">
-        <v>1</v>
-      </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6">
-        <v>1</v>
-      </c>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6">
-        <v>5</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M29" s="6">
-        <v>0</v>
-      </c>
-      <c r="N29" s="6">
-        <v>420</v>
-      </c>
-      <c r="O29" s="6">
-        <v>12</v>
-      </c>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-    </row>
-    <row r="30" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A30" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="5">
-        <v>11003</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E30" s="6">
-        <v>11003</v>
-      </c>
-      <c r="F30" s="6">
-        <v>1</v>
-      </c>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6">
-        <v>1</v>
-      </c>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6">
-        <v>5</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M30" s="6">
-        <v>0</v>
-      </c>
-      <c r="N30" s="6">
-        <v>420</v>
-      </c>
-      <c r="O30" s="6">
-        <v>12</v>
-      </c>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
-    </row>
-    <row r="31" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A31" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="5">
-        <v>11004</v>
-      </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E31" s="6">
-        <v>11004</v>
-      </c>
-      <c r="F31" s="6">
-        <v>1</v>
-      </c>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6">
-        <v>1</v>
-      </c>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6">
-        <v>5</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M31" s="6">
-        <v>0</v>
-      </c>
-      <c r="N31" s="6">
-        <v>420</v>
-      </c>
-      <c r="O31" s="6">
-        <v>12</v>
-      </c>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
-    </row>
-    <row r="32" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A32" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" s="5">
-        <v>11005</v>
-      </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E32" s="6">
-        <v>11005</v>
-      </c>
-      <c r="F32" s="6">
-        <v>1</v>
-      </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6">
-        <v>1</v>
-      </c>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6">
-        <v>5</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M32" s="6">
-        <v>0</v>
-      </c>
-      <c r="N32" s="6">
-        <v>420</v>
-      </c>
-      <c r="O32" s="6">
-        <v>12</v>
-      </c>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-    </row>
-    <row r="33" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A33" s="7"/>
-      <c r="B33" s="6">
-        <v>12001</v>
-      </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E33" s="6">
-        <v>12001</v>
-      </c>
-      <c r="F33" s="6">
-        <v>1</v>
-      </c>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6">
-        <v>1801</v>
-      </c>
-      <c r="I33" s="6">
-        <v>1</v>
-      </c>
-      <c r="J33" s="8">
-        <v>2014</v>
-      </c>
-      <c r="K33" s="6">
+      <c r="O39" s="7">
         <v>10</v>
       </c>
-      <c r="L33" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M33" s="6">
-        <v>0</v>
-      </c>
-      <c r="N33" s="6">
-        <v>420</v>
-      </c>
-      <c r="O33" s="6">
-        <v>10</v>
-      </c>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
-    </row>
-    <row r="34" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A34" s="7"/>
-      <c r="B34" s="6">
-        <v>12002</v>
-      </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E34" s="6">
-        <v>12002</v>
-      </c>
-      <c r="F34" s="6">
-        <v>1</v>
-      </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6">
-        <v>1802</v>
-      </c>
-      <c r="I34" s="6">
-        <v>1</v>
-      </c>
-      <c r="J34" s="8">
-        <v>2014</v>
-      </c>
-      <c r="K34" s="6">
-        <v>10</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M34" s="6">
-        <v>0</v>
-      </c>
-      <c r="N34" s="6">
-        <v>420</v>
-      </c>
-      <c r="O34" s="6">
-        <v>10</v>
-      </c>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
-    </row>
-    <row r="35" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A35" s="7"/>
-      <c r="B35" s="6">
-        <v>12003</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E35" s="6">
-        <v>12003</v>
-      </c>
-      <c r="F35" s="6">
-        <v>1</v>
-      </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6">
-        <v>1803</v>
-      </c>
-      <c r="I35" s="6">
-        <v>1</v>
-      </c>
-      <c r="J35" s="8">
-        <v>2014</v>
-      </c>
-      <c r="K35" s="6">
-        <v>10</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M35" s="6">
-        <v>0</v>
-      </c>
-      <c r="N35" s="6">
-        <v>420</v>
-      </c>
-      <c r="O35" s="6">
-        <v>10</v>
-      </c>
-      <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
-    </row>
-    <row r="36" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A36" s="7"/>
-      <c r="B36" s="6">
-        <v>12004</v>
-      </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E36" s="6">
-        <v>12004</v>
-      </c>
-      <c r="F36" s="6">
-        <v>1</v>
-      </c>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6">
-        <v>1804</v>
-      </c>
-      <c r="I36" s="6">
-        <v>1</v>
-      </c>
-      <c r="J36" s="8">
-        <v>2014</v>
-      </c>
-      <c r="K36" s="6">
-        <v>10</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M36" s="6">
-        <v>0</v>
-      </c>
-      <c r="N36" s="6">
-        <v>420</v>
-      </c>
-      <c r="O36" s="6">
-        <v>10</v>
-      </c>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-    </row>
-    <row r="37" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A37" s="7"/>
-      <c r="B37" s="6">
-        <v>12005</v>
-      </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" s="6">
-        <v>12005</v>
-      </c>
-      <c r="F37" s="6">
-        <v>1</v>
-      </c>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6">
-        <v>1805</v>
-      </c>
-      <c r="I37" s="6">
-        <v>1</v>
-      </c>
-      <c r="J37" s="8">
-        <v>2014</v>
-      </c>
-      <c r="K37" s="6">
-        <v>10</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M37" s="6">
-        <v>0</v>
-      </c>
-      <c r="N37" s="6">
-        <v>420</v>
-      </c>
-      <c r="O37" s="6">
-        <v>10</v>
-      </c>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A38" s="7"/>
-      <c r="B38" s="6">
-        <v>12006</v>
-      </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E38" s="6">
-        <v>12006</v>
-      </c>
-      <c r="F38" s="6">
-        <v>1</v>
-      </c>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6">
-        <v>1806</v>
-      </c>
-      <c r="I38" s="6">
-        <v>1</v>
-      </c>
-      <c r="J38" s="8">
-        <v>2014</v>
-      </c>
-      <c r="K38" s="6">
-        <v>20</v>
-      </c>
-      <c r="L38" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M38" s="6">
-        <v>0</v>
-      </c>
-      <c r="N38" s="6">
-        <v>320</v>
-      </c>
-      <c r="O38" s="6">
-        <v>10</v>
-      </c>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
-    </row>
-    <row r="39" ht="16.5" customHeight="1" spans="1:17">
-      <c r="A39" s="7"/>
-      <c r="B39" s="6">
-        <v>12007</v>
-      </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E39" s="6">
-        <v>12007</v>
-      </c>
-      <c r="F39" s="6">
-        <v>1</v>
-      </c>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6">
-        <v>1807</v>
-      </c>
-      <c r="I39" s="6">
-        <v>1</v>
-      </c>
-      <c r="J39" s="8">
-        <v>2014</v>
-      </c>
-      <c r="K39" s="6">
-        <v>10</v>
-      </c>
-      <c r="L39" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M39" s="6">
-        <v>0</v>
-      </c>
-      <c r="N39" s="6">
-        <v>420</v>
-      </c>
-      <c r="O39" s="6">
-        <v>10</v>
-      </c>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="L4:L1048576">

--- a/RaidenDemo/文档/配置表/BulletResource.xlsx
+++ b/RaidenDemo/文档/配置表/BulletResource.xlsx
@@ -544,7 +544,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -566,12 +566,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF404040"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -939,7 +933,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="3">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
@@ -963,16 +957,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="7">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
@@ -981,85 +975,85 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="39" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="40" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1074,6 +1068,9 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1087,9 +1084,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
@@ -2259,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="7">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="O15" s="7">
         <v>2</v>
